--- a/Employee_Reports_wi48/Manuel Jr. Esplago Feniza Q0279.xlsx
+++ b/Employee_Reports_wi48/Manuel Jr. Esplago Feniza Q0279.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-213</v>
+        <v>-216</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1030,9 +1030,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>18-Mar-2025</t>
@@ -1044,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1093,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1130,11 +1142,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1406,7 +1418,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7639</v>
+        <v>7636</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
